--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2023/Airline_Cumulative_Statistics_2023.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2023/Airline_Cumulative_Statistics_2023.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
   <si>
     <t>Row</t>
   </si>
@@ -25,6 +25,9 @@
   </si>
   <si>
     <t>American</t>
+  </si>
+  <si>
+    <t>Avelo</t>
   </si>
   <si>
     <t>Breeze</t>
@@ -166,7 +169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -189,40 +192,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
@@ -271,19 +274,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>15934620409</v>
+        <v>15935152994</v>
       </c>
       <c r="C3" s="0">
-        <v>18461299152</v>
+        <v>18461913352</v>
       </c>
       <c r="D3" s="0">
-        <v>403879</v>
+        <v>403892</v>
       </c>
       <c r="E3" s="0">
         <v>176</v>
       </c>
       <c r="F3" s="0">
-        <v>116285</v>
+        <v>116289</v>
       </c>
       <c r="G3" s="0">
         <v>2.54</v>
@@ -298,7 +301,7 @@
         <v>898</v>
       </c>
       <c r="K3" s="0">
-        <v>5312.25</v>
+        <v>5312.0600000000004</v>
       </c>
       <c r="L3" s="0">
         <v>30.09</v>
@@ -353,19 +356,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>2199500539</v>
+        <v>1859542406</v>
       </c>
       <c r="C5" s="0">
-        <v>2864472677</v>
+        <v>2389596523</v>
       </c>
       <c r="D5" s="0">
         <v>0</v>
       </c>
       <c r="E5" s="0">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="F5" s="0">
-        <v>21918</v>
+        <v>17824</v>
       </c>
       <c r="G5" s="0">
         <v>0</v>
@@ -374,10 +377,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="0">
-        <v>76.790000000000006</v>
+        <v>77.819999999999993</v>
       </c>
       <c r="J5" s="0">
-        <v>1003</v>
+        <v>791</v>
       </c>
       <c r="K5" s="0">
         <v>0</v>
@@ -394,40 +397,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>219276285138</v>
+        <v>2201733554</v>
       </c>
       <c r="C6" s="0">
-        <v>256187557373</v>
+        <v>2867302388</v>
       </c>
       <c r="D6" s="0">
-        <v>767373</v>
+        <v>0</v>
       </c>
       <c r="E6" s="0">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="F6" s="0">
-        <v>1118899</v>
+        <v>21941</v>
       </c>
       <c r="G6" s="0">
-        <v>3.3500000000000001</v>
+        <v>0</v>
       </c>
       <c r="H6" s="0">
-        <v>10.02</v>
+        <v>0</v>
       </c>
       <c r="I6" s="0">
-        <v>85.590000000000003</v>
+        <v>76.790000000000006</v>
       </c>
       <c r="J6" s="0">
-        <v>1184</v>
+        <v>1003</v>
       </c>
       <c r="K6" s="0">
-        <v>6592.2700000000004</v>
+        <v>0</v>
       </c>
       <c r="L6" s="0">
-        <v>35.140000000000001</v>
+        <v>0</v>
       </c>
       <c r="M6" s="0">
-        <v>0.085999999999999993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -435,40 +438,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>30768436678</v>
+        <v>219276285138</v>
       </c>
       <c r="C7" s="0">
-        <v>37784345072</v>
+        <v>256187557373</v>
       </c>
       <c r="D7" s="0">
-        <v>818197</v>
+        <v>767373</v>
       </c>
       <c r="E7" s="0">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="F7" s="0">
-        <v>188843</v>
+        <v>1118899</v>
       </c>
       <c r="G7" s="0">
-        <v>4.0899999999999999</v>
+        <v>3.3500000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>11.33</v>
+        <v>10.02</v>
       </c>
       <c r="I7" s="0">
-        <v>81.430000000000007</v>
+        <v>85.590000000000003</v>
       </c>
       <c r="J7" s="0">
-        <v>1006</v>
+        <v>1184</v>
       </c>
       <c r="K7" s="0">
-        <v>4901.6800000000003</v>
+        <v>6592.2700000000004</v>
       </c>
       <c r="L7" s="0">
-        <v>24.640000000000001</v>
+        <v>35.140000000000001</v>
       </c>
       <c r="M7" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="8">
@@ -476,40 +479,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>16861017055</v>
+        <v>30768436678</v>
       </c>
       <c r="C8" s="0">
-        <v>20198057398</v>
+        <v>37784345072</v>
       </c>
       <c r="D8" s="0">
-        <v>905742</v>
+        <v>818197</v>
       </c>
       <c r="E8" s="0">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="F8" s="0">
-        <v>84105</v>
+        <v>188843</v>
       </c>
       <c r="G8" s="0">
-        <v>3.77</v>
+        <v>4.0899999999999999</v>
       </c>
       <c r="H8" s="0">
-        <v>9.4600000000000009</v>
+        <v>11.33</v>
       </c>
       <c r="I8" s="0">
-        <v>83.480000000000004</v>
+        <v>81.430000000000007</v>
       </c>
       <c r="J8" s="0">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="K8" s="0">
-        <v>8112.9399999999996</v>
+        <v>4901.6800000000003</v>
       </c>
       <c r="L8" s="0">
-        <v>36.380000000000003</v>
+        <v>24.640000000000001</v>
       </c>
       <c r="M8" s="0">
-        <v>0.085000000000000006</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="9">
@@ -517,40 +520,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>56776931776</v>
+        <v>16861017055</v>
       </c>
       <c r="C9" s="0">
-        <v>68537979627</v>
+        <v>20198057398</v>
       </c>
       <c r="D9" s="0">
-        <v>662395</v>
+        <v>905742</v>
       </c>
       <c r="E9" s="0">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="F9" s="0">
-        <v>348368</v>
+        <v>84105</v>
       </c>
       <c r="G9" s="0">
-        <v>3.3700000000000001</v>
+        <v>3.77</v>
       </c>
       <c r="H9" s="0">
-        <v>10.83</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="I9" s="0">
-        <v>82.840000000000003</v>
+        <v>83.480000000000004</v>
       </c>
       <c r="J9" s="0">
-        <v>1227</v>
+        <v>1009</v>
       </c>
       <c r="K9" s="0">
-        <v>5396.3000000000002</v>
+        <v>8112.9399999999996</v>
       </c>
       <c r="L9" s="0">
-        <v>34.119999999999997</v>
+        <v>36.380000000000003</v>
       </c>
       <c r="M9" s="0">
-        <v>0.087999999999999995</v>
+        <v>0.085000000000000006</v>
       </c>
     </row>
     <row r="10">
@@ -558,40 +561,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>136287720622</v>
+        <v>56776931776</v>
       </c>
       <c r="C10" s="0">
-        <v>170360655398</v>
+        <v>68537979627</v>
       </c>
       <c r="D10" s="0">
-        <v>582888</v>
+        <v>662395</v>
       </c>
       <c r="E10" s="0">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F10" s="0">
-        <v>1459654</v>
+        <v>348368</v>
       </c>
       <c r="G10" s="0">
-        <v>4.9900000000000002</v>
+        <v>3.3700000000000001</v>
       </c>
       <c r="H10" s="0">
-        <v>10.029999999999999</v>
+        <v>10.83</v>
       </c>
       <c r="I10" s="0">
-        <v>80</v>
+        <v>82.840000000000003</v>
       </c>
       <c r="J10" s="0">
-        <v>730</v>
+        <v>1227</v>
       </c>
       <c r="K10" s="0">
-        <v>4762.8500000000004</v>
+        <v>5396.3000000000002</v>
       </c>
       <c r="L10" s="0">
-        <v>29.850000000000001</v>
+        <v>34.119999999999997</v>
       </c>
       <c r="M10" s="0">
-        <v>0.082000000000000003</v>
+        <v>0.087999999999999995</v>
       </c>
     </row>
     <row r="11">
@@ -599,40 +602,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>45227510940</v>
+        <v>136287720622</v>
       </c>
       <c r="C11" s="0">
-        <v>55635577138</v>
+        <v>170360655398</v>
       </c>
       <c r="D11" s="0">
-        <v>763700</v>
+        <v>582888</v>
       </c>
       <c r="E11" s="0">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="F11" s="0">
-        <v>296262</v>
+        <v>1459654</v>
       </c>
       <c r="G11" s="0">
-        <v>4.0700000000000003</v>
+        <v>4.9900000000000002</v>
       </c>
       <c r="H11" s="0">
-        <v>11.039999999999999</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="I11" s="0">
-        <v>81.290000000000006</v>
+        <v>80</v>
       </c>
       <c r="J11" s="0">
-        <v>1012</v>
+        <v>730</v>
       </c>
       <c r="K11" s="0">
-        <v>4715.2600000000002</v>
+        <v>4762.8500000000004</v>
       </c>
       <c r="L11" s="0">
-        <v>25.43</v>
+        <v>29.850000000000001</v>
       </c>
       <c r="M11" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="12">
@@ -640,40 +643,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>5865971459</v>
+        <v>45227510940</v>
       </c>
       <c r="C12" s="0">
-        <v>7321550532</v>
+        <v>55635577138</v>
       </c>
       <c r="D12" s="0">
-        <v>370336</v>
+        <v>763700</v>
       </c>
       <c r="E12" s="0">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F12" s="0">
-        <v>35912</v>
+        <v>296262</v>
       </c>
       <c r="G12" s="0">
-        <v>1.8200000000000001</v>
+        <v>4.0700000000000003</v>
       </c>
       <c r="H12" s="0">
-        <v>5.2599999999999998</v>
+        <v>11.039999999999999</v>
       </c>
       <c r="I12" s="0">
-        <v>80.120000000000005</v>
+        <v>81.290000000000006</v>
       </c>
       <c r="J12" s="0">
-        <v>1109</v>
+        <v>1012</v>
       </c>
       <c r="K12" s="0">
-        <v>5745.1800000000003</v>
+        <v>4715.2600000000002</v>
       </c>
       <c r="L12" s="0">
-        <v>31.25</v>
+        <v>25.43</v>
       </c>
       <c r="M12" s="0">
-        <v>0.082000000000000003</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="13">
@@ -681,40 +684,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>229916409689</v>
+        <v>5865971459</v>
       </c>
       <c r="C13" s="0">
-        <v>274046492919</v>
+        <v>7321550532</v>
       </c>
       <c r="D13" s="0">
-        <v>825267</v>
+        <v>370336</v>
       </c>
       <c r="E13" s="0">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="F13" s="0">
-        <v>910204</v>
+        <v>35912</v>
       </c>
       <c r="G13" s="0">
-        <v>2.7400000000000002</v>
+        <v>1.8200000000000001</v>
       </c>
       <c r="H13" s="0">
-        <v>9.9100000000000001</v>
+        <v>5.2599999999999998</v>
       </c>
       <c r="I13" s="0">
-        <v>83.900000000000006</v>
+        <v>80.120000000000005</v>
       </c>
       <c r="J13" s="0">
-        <v>1491</v>
+        <v>1109</v>
       </c>
       <c r="K13" s="0">
-        <v>7233.4700000000003</v>
+        <v>5745.1800000000003</v>
       </c>
       <c r="L13" s="0">
-        <v>37.009999999999998</v>
+        <v>31.25</v>
       </c>
       <c r="M13" s="0">
-        <v>0.086999999999999994</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="14">
@@ -722,40 +725,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>1239243712</v>
+        <v>229916409689</v>
       </c>
       <c r="C14" s="0">
-        <v>1433920400</v>
+        <v>274046492919</v>
       </c>
       <c r="D14" s="0">
-        <v>70846</v>
+        <v>825267</v>
       </c>
       <c r="E14" s="0">
-        <v>50</v>
+        <v>176</v>
       </c>
       <c r="F14" s="0">
-        <v>72175</v>
+        <v>910204</v>
       </c>
       <c r="G14" s="0">
-        <v>3.5699999999999998</v>
+        <v>2.7400000000000002</v>
       </c>
       <c r="H14" s="0">
-        <v>5.5199999999999996</v>
+        <v>9.9100000000000001</v>
       </c>
       <c r="I14" s="0">
-        <v>86.420000000000002</v>
+        <v>83.900000000000006</v>
       </c>
       <c r="J14" s="0">
-        <v>397</v>
+        <v>1491</v>
       </c>
       <c r="K14" s="0">
-        <v>1709.04</v>
+        <v>7233.4700000000003</v>
       </c>
       <c r="L14" s="0">
-        <v>34.18</v>
+        <v>37.009999999999998</v>
       </c>
       <c r="M14" s="0">
-        <v>0.13300000000000001</v>
+        <v>0.086999999999999994</v>
       </c>
     </row>
     <row r="15">
@@ -763,40 +766,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>5485049614</v>
+        <v>1239243712</v>
       </c>
       <c r="C15" s="0">
-        <v>6729587277</v>
+        <v>1433920400</v>
       </c>
       <c r="D15" s="0">
-        <v>138840</v>
+        <v>70846</v>
       </c>
       <c r="E15" s="0">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="F15" s="0">
-        <v>214222</v>
+        <v>72175</v>
       </c>
       <c r="G15" s="0">
-        <v>4.4199999999999999</v>
+        <v>3.5699999999999998</v>
       </c>
       <c r="H15" s="0">
-        <v>7.1200000000000001</v>
+        <v>5.5199999999999996</v>
       </c>
       <c r="I15" s="0">
-        <v>81.510000000000005</v>
+        <v>86.420000000000002</v>
       </c>
       <c r="J15" s="0">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="K15" s="0">
-        <v>1935.9200000000001</v>
+        <v>1709.04</v>
       </c>
       <c r="L15" s="0">
-        <v>26.059999999999999</v>
+        <v>34.18</v>
       </c>
       <c r="M15" s="0">
-        <v>0.099000000000000005</v>
+        <v>0.13300000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -804,40 +807,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>7891087096</v>
+        <v>5485049614</v>
       </c>
       <c r="C16" s="0">
-        <v>9674418267</v>
+        <v>6729587277</v>
       </c>
       <c r="D16" s="0">
-        <v>67545</v>
+        <v>138840</v>
       </c>
       <c r="E16" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16" s="0">
-        <v>241425</v>
+        <v>214222</v>
       </c>
       <c r="G16" s="0">
-        <v>1.6899999999999999</v>
+        <v>4.4199999999999999</v>
       </c>
       <c r="H16" s="0">
-        <v>3.0499999999999998</v>
+        <v>7.1200000000000001</v>
       </c>
       <c r="I16" s="0">
-        <v>81.569999999999993</v>
+        <v>81.510000000000005</v>
       </c>
       <c r="J16" s="0">
-        <v>541</v>
+        <v>422</v>
       </c>
       <c r="K16" s="0">
-        <v>2158.5500000000002</v>
+        <v>1935.9200000000001</v>
       </c>
       <c r="L16" s="0">
-        <v>29.289999999999999</v>
+        <v>26.059999999999999</v>
       </c>
       <c r="M16" s="0">
-        <v>0.097000000000000003</v>
+        <v>0.099000000000000005</v>
       </c>
     </row>
     <row r="17">
@@ -845,40 +848,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>606963891</v>
+        <v>7891087096</v>
       </c>
       <c r="C17" s="0">
-        <v>735124450</v>
+        <v>9674418267</v>
       </c>
       <c r="D17" s="0">
-        <v>30066</v>
+        <v>67545</v>
       </c>
       <c r="E17" s="0">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F17" s="0">
-        <v>45438</v>
+        <v>241425</v>
       </c>
       <c r="G17" s="0">
-        <v>1.8600000000000001</v>
+        <v>1.6899999999999999</v>
       </c>
       <c r="H17" s="0">
-        <v>2.8100000000000001</v>
+        <v>3.0499999999999998</v>
       </c>
       <c r="I17" s="0">
-        <v>82.569999999999993</v>
+        <v>81.569999999999993</v>
       </c>
       <c r="J17" s="0">
-        <v>324</v>
+        <v>541</v>
       </c>
       <c r="K17" s="0">
-        <v>2810.73</v>
+        <v>2158.5500000000002</v>
       </c>
       <c r="L17" s="0">
-        <v>56.210000000000001</v>
+        <v>29.289999999999999</v>
       </c>
       <c r="M17" s="0">
-        <v>0.26200000000000001</v>
+        <v>0.097000000000000003</v>
       </c>
     </row>
     <row r="18">
@@ -886,40 +889,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>2129212501</v>
+        <v>606963891</v>
       </c>
       <c r="C18" s="0">
-        <v>2568132872</v>
+        <v>735124450</v>
       </c>
       <c r="D18" s="0">
-        <v>193529</v>
+        <v>30066</v>
       </c>
       <c r="E18" s="0">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="F18" s="0">
-        <v>69906</v>
+        <v>45438</v>
       </c>
       <c r="G18" s="0">
-        <v>5.2699999999999996</v>
+        <v>1.8600000000000001</v>
       </c>
       <c r="H18" s="0">
-        <v>8.4000000000000004</v>
+        <v>2.8100000000000001</v>
       </c>
       <c r="I18" s="0">
-        <v>82.909999999999997</v>
+        <v>82.569999999999993</v>
       </c>
       <c r="J18" s="0">
-        <v>483</v>
+        <v>324</v>
       </c>
       <c r="K18" s="0">
-        <v>1746.46</v>
+        <v>2810.73</v>
       </c>
       <c r="L18" s="0">
-        <v>22.98</v>
+        <v>56.210000000000001</v>
       </c>
       <c r="M18" s="0">
-        <v>0.075999999999999998</v>
+        <v>0.26200000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -927,40 +930,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>3423149052</v>
+        <v>2134573471</v>
       </c>
       <c r="C19" s="0">
-        <v>4089018798</v>
+        <v>2574967324</v>
       </c>
       <c r="D19" s="0">
-        <v>175947</v>
+        <v>191590</v>
       </c>
       <c r="E19" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F19" s="0">
-        <v>100082</v>
+        <v>70415</v>
       </c>
       <c r="G19" s="0">
-        <v>4.3099999999999996</v>
+        <v>5.2400000000000002</v>
       </c>
       <c r="H19" s="0">
-        <v>7.7400000000000002</v>
+        <v>8.3399999999999999</v>
       </c>
       <c r="I19" s="0">
-        <v>83.719999999999999</v>
+        <v>82.900000000000006</v>
       </c>
       <c r="J19" s="0">
-        <v>541</v>
+        <v>481</v>
       </c>
       <c r="K19" s="0">
-        <v>2079.23</v>
+        <v>1860.79</v>
       </c>
       <c r="L19" s="0">
-        <v>27.550000000000001</v>
+        <v>24.48</v>
       </c>
       <c r="M19" s="0">
-        <v>0.090999999999999998</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="20">
@@ -968,40 +971,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>1280029323</v>
+        <v>3423149052</v>
       </c>
       <c r="C20" s="0">
-        <v>1529120824</v>
+        <v>4089018798</v>
       </c>
       <c r="D20" s="0">
-        <v>72402</v>
+        <v>175947</v>
       </c>
       <c r="E20" s="0">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F20" s="0">
-        <v>104456</v>
+        <v>100082</v>
       </c>
       <c r="G20" s="0">
-        <v>4.9500000000000002</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="H20" s="0">
-        <v>7.0599999999999996</v>
+        <v>7.7400000000000002</v>
       </c>
       <c r="I20" s="0">
-        <v>83.709999999999994</v>
+        <v>83.719999999999999</v>
       </c>
       <c r="J20" s="0">
-        <v>293</v>
+        <v>541</v>
       </c>
       <c r="K20" s="0">
-        <v>2292.46</v>
+        <v>2140.6599999999999</v>
       </c>
       <c r="L20" s="0">
-        <v>45.850000000000001</v>
+        <v>28.370000000000001</v>
       </c>
       <c r="M20" s="0">
-        <v>0.223</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="21">
@@ -1009,40 +1012,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>4995828320</v>
+        <v>1280029323</v>
       </c>
       <c r="C21" s="0">
-        <v>6112355699</v>
+        <v>1529120824</v>
       </c>
       <c r="D21" s="0">
-        <v>142016</v>
+        <v>72402</v>
       </c>
       <c r="E21" s="0">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="F21" s="0">
-        <v>197269</v>
+        <v>104456</v>
       </c>
       <c r="G21" s="0">
-        <v>4.5800000000000001</v>
+        <v>4.9500000000000002</v>
       </c>
       <c r="H21" s="0">
-        <v>7.5700000000000003</v>
+        <v>7.0599999999999996</v>
       </c>
       <c r="I21" s="0">
-        <v>81.730000000000004</v>
+        <v>83.709999999999994</v>
       </c>
       <c r="J21" s="0">
-        <v>428</v>
+        <v>293</v>
       </c>
       <c r="K21" s="0">
-        <v>2491.0799999999999</v>
+        <v>2292.46</v>
       </c>
       <c r="L21" s="0">
-        <v>34.439999999999998</v>
+        <v>45.850000000000001</v>
       </c>
       <c r="M21" s="0">
-        <v>0.13300000000000001</v>
+        <v>0.223</v>
       </c>
     </row>
     <row r="22">
@@ -1050,40 +1053,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>8546315512</v>
+        <v>4995828320</v>
       </c>
       <c r="C22" s="0">
-        <v>11103075210</v>
+        <v>6112355699</v>
       </c>
       <c r="D22" s="0">
-        <v>136217</v>
+        <v>142016</v>
       </c>
       <c r="E22" s="0">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F22" s="0">
-        <v>308857</v>
+        <v>197269</v>
       </c>
       <c r="G22" s="0">
-        <v>3.79</v>
+        <v>4.5800000000000001</v>
       </c>
       <c r="H22" s="0">
-        <v>6.8899999999999997</v>
+        <v>7.5700000000000003</v>
       </c>
       <c r="I22" s="0">
-        <v>76.969999999999999</v>
+        <v>81.730000000000004</v>
       </c>
       <c r="J22" s="0">
-        <v>483</v>
+        <v>428</v>
       </c>
       <c r="K22" s="0">
-        <v>1740.48</v>
+        <v>2491.0799999999999</v>
       </c>
       <c r="L22" s="0">
-        <v>23.41</v>
+        <v>34.439999999999998</v>
       </c>
       <c r="M22" s="0">
-        <v>0.087999999999999995</v>
+        <v>0.13300000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1091,40 +1094,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>18132203156</v>
+        <v>8546315512</v>
       </c>
       <c r="C23" s="0">
-        <v>22136904081</v>
+        <v>11103075210</v>
       </c>
       <c r="D23" s="0">
-        <v>107055</v>
+        <v>136217</v>
       </c>
       <c r="E23" s="0">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F23" s="0">
-        <v>698026</v>
+        <v>308857</v>
       </c>
       <c r="G23" s="0">
-        <v>3.3799999999999999</v>
+        <v>3.79</v>
       </c>
       <c r="H23" s="0">
-        <v>5.5700000000000003</v>
+        <v>6.8899999999999997</v>
       </c>
       <c r="I23" s="0">
-        <v>81.909999999999997</v>
+        <v>76.969999999999999</v>
       </c>
       <c r="J23" s="0">
-        <v>454</v>
+        <v>483</v>
       </c>
       <c r="K23" s="0">
-        <v>1781.6099999999999</v>
+        <v>1740.48</v>
       </c>
       <c r="L23" s="0">
-        <v>25.710000000000001</v>
+        <v>23.41</v>
       </c>
       <c r="M23" s="0">
-        <v>0.092999999999999999</v>
+        <v>0.087999999999999995</v>
       </c>
     </row>
     <row r="24">
@@ -1132,40 +1135,81 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>1075495737674</v>
+        <v>18132203156</v>
       </c>
       <c r="C24" s="0">
-        <v>1290645368239</v>
+        <v>22136904081</v>
       </c>
       <c r="D24" s="0">
-        <v>556946</v>
+        <v>107055</v>
       </c>
       <c r="E24" s="0">
+        <v>69</v>
+      </c>
+      <c r="F24" s="0">
+        <v>698026</v>
+      </c>
+      <c r="G24" s="0">
+        <v>3.3799999999999999</v>
+      </c>
+      <c r="H24" s="0">
+        <v>5.5700000000000003</v>
+      </c>
+      <c r="I24" s="0">
+        <v>81.909999999999997</v>
+      </c>
+      <c r="J24" s="0">
+        <v>454</v>
+      </c>
+      <c r="K24" s="0">
+        <v>1781.6099999999999</v>
+      </c>
+      <c r="L24" s="0">
+        <v>25.710000000000001</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.092999999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>1077363406650</v>
+      </c>
+      <c r="C25" s="0">
+        <v>1293045243125</v>
+      </c>
+      <c r="D25" s="0">
+        <v>557941</v>
+      </c>
+      <c r="E25" s="0">
         <v>144</v>
       </c>
-      <c r="F24" s="0">
-        <v>8038577</v>
-      </c>
-      <c r="G24" s="0">
-        <v>3.4700000000000002</v>
-      </c>
-      <c r="H24" s="0">
-        <v>8.8200000000000003</v>
-      </c>
-      <c r="I24" s="0">
-        <v>83.329999999999998</v>
-      </c>
-      <c r="J24" s="0">
-        <v>937</v>
-      </c>
-      <c r="K24" s="0">
-        <v>5468.8299999999999</v>
-      </c>
-      <c r="L24" s="0">
-        <v>33.640000000000001</v>
-      </c>
-      <c r="M24" s="0">
-        <v>0.086999999999999994</v>
+      <c r="F25" s="0">
+        <v>8056937</v>
+      </c>
+      <c r="G25" s="0">
+        <v>3.48</v>
+      </c>
+      <c r="H25" s="0">
+        <v>8.8300000000000001</v>
+      </c>
+      <c r="I25" s="0">
+        <v>83.319999999999993</v>
+      </c>
+      <c r="J25" s="0">
+        <v>936</v>
+      </c>
+      <c r="K25" s="0">
+        <v>5459.0799999999999</v>
+      </c>
+      <c r="L25" s="0">
+        <v>33.579999999999998</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.085999999999999993</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2023/Airline_Cumulative_Statistics_2023.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2023/Airline_Cumulative_Statistics_2023.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="41" uniqueCount="41">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -169,7 +181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -192,40 +204,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
@@ -1176,39 +1188,203 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>658866863670</v>
+      </c>
+      <c r="C25" s="0">
+        <v>780034584419</v>
+      </c>
+      <c r="D25" s="0">
+        <v>773092</v>
+      </c>
+      <c r="E25" s="0">
+        <v>173</v>
+      </c>
+      <c r="F25" s="0">
+        <v>3173848</v>
+      </c>
+      <c r="G25" s="0">
+        <v>3.1499999999999999</v>
+      </c>
+      <c r="H25" s="0">
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="I25" s="0">
+        <v>84.469999999999999</v>
+      </c>
+      <c r="J25" s="0">
+        <v>1259</v>
+      </c>
+      <c r="K25" s="0">
+        <v>6999.1300000000001</v>
+      </c>
+      <c r="L25" s="0">
+        <v>36.960000000000001</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.089999999999999997</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>265105485356</v>
+      </c>
+      <c r="C26" s="0">
+        <v>325299183759</v>
+      </c>
+      <c r="D26" s="0">
+        <v>652530</v>
+      </c>
+      <c r="E26" s="0">
+        <v>159</v>
+      </c>
+      <c r="F26" s="0">
+        <v>2175594</v>
+      </c>
+      <c r="G26" s="0">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="H26" s="0">
+        <v>10.51</v>
+      </c>
+      <c r="I26" s="0">
+        <v>81.5</v>
+      </c>
+      <c r="J26" s="0">
+        <v>904</v>
+      </c>
+      <c r="K26" s="0">
+        <v>5017.8100000000004</v>
+      </c>
+      <c r="L26" s="0">
+        <v>30.670000000000002</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.081000000000000003</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>99656614477</v>
+      </c>
+      <c r="C27" s="0">
+        <v>121592982617</v>
+      </c>
+      <c r="D27" s="0">
+        <v>659005</v>
+      </c>
+      <c r="E27" s="0">
+        <v>187</v>
+      </c>
+      <c r="F27" s="0">
+        <v>655130</v>
+      </c>
+      <c r="G27" s="0">
+        <v>3.5499999999999998</v>
+      </c>
+      <c r="H27" s="0">
+        <v>9.4900000000000002</v>
+      </c>
+      <c r="I27" s="0">
+        <v>81.959999999999994</v>
+      </c>
+      <c r="J27" s="0">
+        <v>990</v>
+      </c>
+      <c r="K27" s="0">
+        <v>4818.3299999999999</v>
+      </c>
+      <c r="L27" s="0">
+        <v>25.690000000000001</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.069000000000000006</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>53734443147</v>
+      </c>
+      <c r="C28" s="0">
+        <v>66118492330</v>
+      </c>
+      <c r="D28" s="0">
+        <v>105702</v>
+      </c>
+      <c r="E28" s="0">
+        <v>70</v>
+      </c>
+      <c r="F28" s="0">
+        <v>2052365</v>
+      </c>
+      <c r="G28" s="0">
+        <v>3.2799999999999998</v>
+      </c>
+      <c r="H28" s="0">
+        <v>5.5</v>
+      </c>
+      <c r="I28" s="0">
+        <v>81.269999999999996</v>
+      </c>
+      <c r="J28" s="0">
+        <v>455</v>
+      </c>
+      <c r="K28" s="0">
+        <v>1966.8800000000001</v>
+      </c>
+      <c r="L28" s="0">
+        <v>28.039999999999999</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.10199999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>1077363406650</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>1293045243125</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>557941</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>144</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>8056937</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G29" s="0">
         <v>3.48</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H29" s="0">
         <v>8.8300000000000001</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>83.319999999999993</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>936</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>5459.0799999999999</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>33.579999999999998</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>0.085999999999999993</v>
       </c>
     </row>
